--- a/artfynd/A 23931-2024 artfynd.xlsx
+++ b/artfynd/A 23931-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102536229</v>
+        <v>113220516</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsen, Jmt</t>
+          <t>Gissmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544983.2524337303</v>
+        <v>545022</v>
       </c>
       <c r="R2" t="n">
-        <v>7007654.462994433</v>
+        <v>7007667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,57 +743,47 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113220518</v>
+        <v>113220522</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544960</v>
+        <v>544928</v>
       </c>
       <c r="R3" t="n">
-        <v>7007653</v>
+        <v>7007667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,21 +861,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -911,16 +884,11 @@
         <v>113220525</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1029,15 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113220513</v>
+        <v>118280238</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544943</v>
+        <v>544762</v>
       </c>
       <c r="R5" t="n">
-        <v>7007608</v>
+        <v>7007677</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,31 +1082,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113220522</v>
+        <v>102536229</v>
       </c>
       <c r="B6" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gissmyrberget, Jmt</t>
+          <t>Åsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544928</v>
+        <v>544983</v>
       </c>
       <c r="R6" t="n">
-        <v>7007667</v>
+        <v>7007655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,12 +1163,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,17 +1183,759 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113220518</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gissmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>544960</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7007653</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113220526</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gissmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>545018</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7007665</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113220513</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gissmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>544943</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7007608</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113220517</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gissmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>545022</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7007667</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113220514</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gissmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>545050</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7007551</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113220515</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gissmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>545050</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7007551</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118280225</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gissmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>544931</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7007728</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>på gammal vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 23931-2024 artfynd.xlsx
+++ b/artfynd/A 23931-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118280238</t>
         </is>
       </c>
     </row>
@@ -878,6 +888,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220516</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220522</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220525</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102536229</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220518</t>
         </is>
       </c>
     </row>
@@ -1428,6 +1463,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220526</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220513</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220517</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220514</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220515</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,8 +1998,27 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118280225</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>